--- a/stories/arbres/TREE-SEC-013.xlsx
+++ b/stories/arbres/TREE-SEC-013.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Nino est à la ferme avec Maman. C'est la maison des champs. Nino a des jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. On appelle Maman. Papa range le lait.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Nino joue. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. Une vache meugle loin. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Ça sent le foin. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. L'eau coule. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Le bois craque. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. L'eau coule. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le lait tinte dans le seau. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. Ça sent le foin. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Nino joue. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6725,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6902,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7093,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. L'eau coule. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. L'eau coule. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le lait tinte dans le seau. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Un oiseau chante. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. Le lait tinte dans le seau. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Le lait tinte dans le seau. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Une vache meugle loin. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le bois craque. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Nino range. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11581,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11758,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11949,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. Une vache meugle loin. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Le bois craque. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Le lait tinte dans le seau. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Une vache meugle loin. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le bois craque. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. Ça sent le foin. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Une vache meugle loin. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Le bois craque. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Ça sent le foin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16117,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-013.xlsx
+++ b/stories/arbres/TREE-SEC-013.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Nino est à la ferme avec Maman. C'est la maison des champs. Nino a des jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. On appelle Maman. Papa range le lait.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|C'est le matin. Nino joue. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Nino a choisi la cuisine. Une vache meugle loin. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|Nino prend le ballon rouge. Ça sent le foin. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|Nino prend le seau bleu. L'eau coule. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Nino a choisi le jardin. Le bois craque. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3980,6 +4000,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4151,6 +4172,7 @@
           <t>narrateur|Nino prend le ballon rouge. L'eau coule. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4512,7 @@
           <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4852,7 @@
           <t>narrateur|Nino prend le doudou. Le lait tinte dans le seau. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5192,7 @@
           <t>narrateur|Nino a choisi la chambre. Ça sent le foin. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5356,6 +5384,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5527,6 +5556,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5896,7 @@
           <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6236,7 @@
           <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6576,7 @@
           <t>narrateur|C'est après la sieste. Nino joue. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6732,6 +6768,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6907,6 +6944,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7136,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7308,7 @@
           <t>narrateur|Nino a choisi la cuisine. L'eau coule. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7460,6 +7500,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7631,6 +7672,7 @@
           <t>narrateur|Nino prend le ballon rouge. L'eau coule. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8012,7 @@
           <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8180,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8352,7 @@
           <t>narrateur|Nino prend le doudou. Le lait tinte dans le seau. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8692,7 @@
           <t>narrateur|Nino a choisi le jardin. Un oiseau chante. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8836,6 +8884,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9007,6 +9056,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9396,7 @@
           <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9736,7 @@
           <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10076,7 @@
           <t>narrateur|Nino a choisi la chambre. Le lait tinte dans le seau. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,6 +10268,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10383,6 +10440,7 @@
           <t>narrateur|Nino prend le ballon rouge. Le lait tinte dans le seau. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10780,7 @@
           <t>narrateur|Nino prend le seau bleu. Une vache meugle loin. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11120,7 @@
           <t>narrateur|Nino prend le doudou. Le bois craque. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11460,7 @@
           <t>narrateur|C'est le soir. Nino range. Les mains restent avec les jouets. Il appelle un adulte. Il appelle Maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11588,6 +11652,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11763,6 +11828,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12020,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12192,7 @@
           <t>narrateur|Nino a choisi la cuisine. Une vache meugle loin. Ils sont dans la cuisine. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12316,6 +12384,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12487,6 +12556,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12896,7 @@
           <t>narrateur|Nino prend le seau bleu. Le lait tinte dans le seau. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13236,7 @@
           <t>narrateur|Nino prend le doudou. Une vache meugle loin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13576,7 @@
           <t>narrateur|Nino a choisi le jardin. Le bois craque. Ils sont près du jardin, dans la maison. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13692,6 +13768,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13863,6 +13940,7 @@
           <t>narrateur|Nino prend le ballon rouge. Le lait tinte dans le seau. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14108,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14280,7 @@
           <t>narrateur|Nino prend le seau bleu. Une vache meugle loin. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14620,7 @@
           <t>narrateur|Nino prend le doudou. Le bois craque. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +14960,7 @@
           <t>narrateur|Nino a choisi la chambre. Ça sent le foin. Ils sont dans la chambre. Les mains restent avec les jouets. On appelle un adulte. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15068,6 +15152,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15239,6 +15324,7 @@
           <t>narrateur|Nino prend le ballon rouge. Une vache meugle loin. Nino tient le ballon rouge. Mains avec les jouets. Il appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15664,7 @@
           <t>narrateur|Nino prend le seau bleu. Le bois craque. Nino tient le seau bleu. Mains avec les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16004,7 @@
           <t>narrateur|Nino prend le doudou. Ça sent le foin. Nino tient le doudou. Mains avec les jouets. Il appelle Maman, l'adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16215,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16325,6 +16430,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
